--- a/catalogo_heart_graphic.xlsx
+++ b/catalogo_heart_graphic.xlsx
@@ -18,10 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-  </numFmts>
-  <fonts count="6">
+  <numFmts count="0"/>
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +39,11 @@
       <sz val="10"/>
     </font>
     <font>
+      <name val="Consolas"/>
+      <color rgb="003A3550"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="003A3550"/>
@@ -49,17 +52,28 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="003A3550"/>
+      <color rgb="007A5FD0"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="007A5FD0"/>
-      <sz val="14"/>
+      <color rgb="003A3550"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="001F6F8B"/>
+      <sz val="9.5"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -78,12 +92,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFF3B0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF6C9"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -91,24 +105,14 @@
         <fgColor rgb="00CDB8F9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F1EAFE"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00DDD6F0"/>
-      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -117,37 +121,41 @@
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -515,16 +523,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="56" customWidth="1" min="9" max="9"/>
+    <col width="64" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,26 +557,46 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>notas</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>imagen_principal</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>galeria</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>colores</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>cantidades</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>activo</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="78" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -578,24 +610,49 @@
           <t>☕</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Tazón de 11 onzas personalizado con tu diseño favorito.</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Valores por mayor no válidos para tazones de colores/especiales (valor único $4.000) · Colores: blanco, rojo, verde, celeste, rosado y amarillo (mango e interior de color) · Diseño gratis</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "0": {"Color_hex":"#ffffff", "Color_name":"Blanco", "url_img":""},
+  "1": {"Color_hex":"#f23b3b", "Color_name":"Rojo", "url_img":""},
+  "2": {"Color_hex":"#12b653", "Color_name":"Verde", "url_img":""},
+  "3": {"Color_hex":"#25b6ee", "Color_name":"Azul", "url_img":""},
+  "4": {"Color_hex":"#f9a8dd", "Color_name":"Rosado", "url_img":""},
+  "5": {"Color_hex":"#ffd34d", "Color_name":"Amarillo", "url_img":""}
+}</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "11 Onzas": [{"unidades":1, "precio":4000}, {"unidades":5, "precio":18500}, {"unidades":20, "precio":50000}, {"unidades":30, "precio":60000}]
+}</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="78" customHeight="1">
       <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
@@ -609,24 +666,41 @@
           <t>🌟</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Stickers troquelados full color, máxima calidad de impresión.</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Para forma personalizada se requiere previa cotización · Adhesivo 135gr, full impresión · Diseño gratis</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "3x3 cm": [{"unidades":100, "precio":4000}, {"unidades":500, "precio":13000}, {"unidades":1000, "precio":22500}, {"unidades":2000, "precio":37500}],
+  "4x4 cm": [{"unidades":100, "precio":5500}, {"unidades":500, "precio":19950}, {"unidades":1000, "precio":35700}, {"unidades":2000, "precio":42000}],
+  "5x5 cm": [{"unidades":100, "precio":7000}, {"unidades":500, "precio":25000}, {"unidades":1000, "precio":38000}, {"unidades":2000, "precio":48000}],
+  "6x6 cm": [{"unidades":100, "precio":9500}, {"unidades":500, "precio":27500}, {"unidades":1000, "precio":42000}, {"unidades":2000, "precio":55900}]
+}</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="78" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -640,24 +714,40 @@
           <t>📄</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Flyers en papel fotográfico full color para tu negocio.</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Gramaje del papel: 135gr · Full impresiones, máxima calidad · Diseño gratis</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Fotográfico 10x14,5": [{"unidades":500, "precio":24000}, {"unidades":1000, "precio":36000}, {"unidades":2000, "precio":60000}, {"unidades":4000, "precio":110000}, {"unidades":8000, "precio":155000}],
+  "Fotográfico 20x14,5": [{"unidades":500, "precio":27000}, {"unidades":1000, "precio":40000}, {"unidades":2000, "precio":57000}, {"unidades":4000, "precio":120000}, {"unidades":8000, "precio":162000}],
+  "Mini Flyer 10x7,25": [{"unidades":500, "precio":18000}, {"unidades":1000, "precio":27000}, {"unidades":2000, "precio":38000}, {"unidades":4000, "precio":63000}, {"unidades":8000, "precio":110000}]
+}</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="78" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
@@ -671,24 +761,39 @@
           <t>💳</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Tarjetas de 9x5,5 cm en opalina lisa full color.</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Gramaje del papel: 250gr · Opalina lisa, full color · Tamaño 9x5,5 cm · Diseño gratis</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "1 Cara": [{"unidades":100, "precio":8000}, {"unidades":200, "precio":14000}, {"unidades":500, "precio":25000}, {"unidades":1000, "precio":35000}, {"unidades":2000, "precio":55000}],
+  "2 Caras": [{"unidades":100, "precio":16000}, {"unidades":200, "precio":20000}, {"unidades":500, "precio":30000}, {"unidades":1000, "precio":48000}, {"unidades":2000, "precio":68000}]
+}</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="78" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -702,24 +807,39 @@
           <t>🧲</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Imanes publicitarios para que nunca te olviden.</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Grosor del imán: 0,4 · Adhesivo fotográfico full color · Diseño gratis</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Simple 5x5,5 cm": [{"unidades":100, "precio":13000}, {"unidades":300, "precio":25000}, {"unidades":500, "precio":40000}, {"unidades":1000, "precio":63000}, {"unidades":2000, "precio":110000}],
+  "Grande 10x5,5 cm": [{"unidades":100, "precio":21000}, {"unidades":300, "precio":45000}, {"unidades":500, "precio":65000}, {"unidades":1000, "precio":110000}, {"unidades":2000, "precio":185000}]
+}</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="78" customHeight="1">
       <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
@@ -733,24 +853,49 @@
           <t>📋</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>vet,general</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Talonarios de 100 hojas, papel bond encolado full color.</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>100 hojas por talonario · Papel bond encolado, impresión alta calidad · Diseño gratis</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>06_talonario_recetario.webp</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>[
+  "06_talonario_recetario.webp"
+]</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Media Carta 14x21,6": [{"unidades":2, "precio":10000}, {"unidades":5, "precio":22000}, {"unidades":10, "precio":35000}, {"unidades":20, "precio":52000}, {"unidades":50, "precio":97000}],
+  "Carta 21,6x27,9": [{"unidades":1, "precio":10000}, {"unidades":2, "precio":18000}, {"unidades":5, "precio":30000}, {"unidades":10, "precio":50000}, {"unidades":20, "precio":85000}]
+}</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="78" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -764,24 +909,59 @@
           <t>🐾</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>vet</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Carnets de vacunas para veterinarias y mascotas regalonas.</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>La medida indicada corresponde al carnet abierto · Papel 250gr, opalina lisa full color · Diseño gratis</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>07_carnet_de_vacunacion.webp</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>[
+  "07_carnet_de_vacunacion.webp",
+  "carnets_veterinarios/carnet_01.webp",
+  "carnets_veterinarios/carnet_02.webp",
+  "carnets_veterinarios/carnet_03.webp",
+  "carnets_veterinarios/carnet_04.webp",
+  "carnets_veterinarios/carnet_05.webp",
+  "carnets_veterinarios/carnet_06.webp",
+  "carnets_veterinarios/carnet_07.webp",
+  "carnets_veterinarios/carnet_08.webp",
+  "carnets_veterinarios/carnet_09.webp",
+  "carnets_veterinarios/carnet_10.webp"
+]</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Mini Carnet 20x14,5": [{"unidades":50, "precio":16000}, {"unidades":100, "precio":26000}, {"unidades":200, "precio":42000}, {"unidades":300, "precio":51000}],
+  "Maxi Carnet 21x27": [{"unidades":50, "precio":18500}, {"unidades":100, "precio":35000}, {"unidades":200, "precio":60000}, {"unidades":300, "precio":80000}]
+}</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="78" customHeight="1">
       <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
@@ -795,24 +975,41 @@
           <t>🛍️</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Bolsas de papel kraft blanca personalizadas full color.</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Bolsa kraft blanca personalizada full color · Con manilla · Biodegradables · Solo color blanco disponible</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Talla S 22x30": [{"unidades":30, "precio":15100}, {"unidades":50, "precio":24500}, {"unidades":100, "precio":47500}, {"unidades":200, "precio":76000}],
+  "Talla M 30x32": [{"unidades":30, "precio":18100}, {"unidades":50, "precio":29500}, {"unidades":100, "precio":55000}, {"unidades":200, "precio":98000}],
+  "Talla L 30x41": [{"unidades":30, "precio":21100}, {"unidades":50, "precio":34000}, {"unidades":100, "precio":65000}, {"unidades":200, "precio":114000}],
+  "Talla XL 38x48": [{"unidades":30, "precio":26850}, {"unidades":50, "precio":42000}, {"unidades":100, "precio":80000}, {"unidades":200, "precio":140000}]
+}</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="78" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -826,24 +1023,39 @@
           <t>🎀</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Stickers de cierre con QR personalizado para tus pedidos.</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Puede incluir QR personalizado (redes sociales, contactos, agradecimiento) · Adhesivo brillante troquelado · Diseño gratis</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "3,5 x 10 cm": [{"unidades":100, "precio":10000}, {"unidades":300, "precio":19000}],
+  "5 x 10 cm": [{"unidades":100, "precio":14000}, {"unidades":300, "precio":25000}]
+}</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="78" customHeight="1">
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
@@ -857,24 +1069,48 @@
           <t>💖</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Tarjetas de fidelización con sus stickers para timbrar.</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Tarjetas de 9x5,5 cm y stickers de 1,5 cm de diámetro · Diseño gratis</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>10_tarjetas_cliente_frecuente.webp</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>[
+  "10_tarjetas_cliente_frecuente.webp"
+]</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Tarjeta + Stickers": [{"unidades":100, "precio":19500}, {"unidades":300, "precio":28000}]
+}</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="78" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -888,24 +1124,48 @@
           <t>📦</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Stickers con datos de envío para tus paquetos.</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Papel adhesivo glossy 135gr · Full color · Diseño gratis</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>11_sticker_de_envio.webp</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>[
+  "11_sticker_de_envio.webp"
+]</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "10 x 8 cm": [{"unidades":100, "precio":13000}, {"unidades":300, "precio":25000}]
+}</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="78" customHeight="1">
       <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
@@ -919,24 +1179,36 @@
           <t>😺</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Chapitas metálicas con el diseño que quieras.</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Diseño gratis al solicitar nuestro servicio</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>[{"unidades":10, "precio":5000}, {"unidades":20, "precio":8600}, {"unidades":30, "precio":11100}, {"unidades":50, "precio":15000}, {"unidades":100, "precio":26000}]</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="78" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -950,24 +1222,36 @@
           <t>🪪</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>vet,general</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Credenciales de PVC para tu equipo o institución.</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Plástico PVC · Diseño gratis</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>[{"unidades":1, "precio":3000}, {"unidades":10, "precio":25000}, {"unidades":20, "precio":40000}, {"unidades":30, "precio":53000}]</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="78" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
@@ -981,24 +1265,36 @@
           <t>🐱</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>vet</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>La cédula chilena de tu mascota, igualita a la real.</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Plástico PVC · Diseño ambos lados</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>[{"unidades":1, "precio":3000}, {"unidades":2, "precio":5000}]</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="78" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -1012,24 +1308,36 @@
           <t>🦴</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>vet</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Placas rígidas con forma y nombre para tu mascota.</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Plástico PVC rígido · Diseño ambos lados</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>[{"unidades":1, "precio":3000}, {"unidades":2, "precio":5000}]</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="78" customHeight="1">
       <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
@@ -1043,24 +1351,40 @@
           <t>👕</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Cinta espiga sublimada con tu marca para tus prendas.</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>Cinta espiga blanca sublimada · Full color personalizada · Diseño gratis</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Espiga 1,5 cm": [{"unidades":30, "precio":3500}, {"unidades":50, "precio":5000}, {"unidades":100, "precio":8000}, {"unidades":300, "precio":18000}, {"unidades":500, "precio":23500}],
+  "Espiga 2 cm": [{"unidades":30, "precio":4500}, {"unidades":50, "precio":6000}, {"unidades":100, "precio":9500}, {"unidades":300, "precio":20400}, {"unidades":500, "precio":25000}],
+  "Espiga 2,5 cm": [{"unidades":30, "precio":5500}, {"unidades":50, "precio":7000}, {"unidades":100, "precio":11500}, {"unidades":300, "precio":22500}, {"unidades":500, "precio":27500}]
+}</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="78" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1074,24 +1398,48 @@
           <t>🎵</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Tu canción favorita estampada directo al vidrio.</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>Precio único · Estampado directo al vidrio · Stock rotativo</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>17_cuadro_spotify.webp</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>[
+  "17_cuadro_spotify.webp"
+]</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "16 x 11 cm": [{"unidades":1, "precio":12000}]
+}</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="78" customHeight="1">
       <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
@@ -1105,24 +1453,38 @@
           <t>🎒</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Morral blanco con cordones ajustables para estampar.</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>Solo color blanco · Talla estándar · Cordones ajustables · 100% poliéster</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "Unidad": [{"unidades":1, "precio":1800}]
+}</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="78" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -1136,24 +1498,48 @@
           <t>🖱️</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Mousepad de 21x17 cm con tu diseño motivacional.</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Sobre las 10 unidades: $2.500 c/u · Diseño gratis</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>19_mousepad.webp</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>[
+  "19_mousepad.webp"
+]</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "21 x 17 cm": [{"unidades":1, "precio":3000}, {"unidades":10, "precio":25000}]
+}</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="78" customHeight="1">
       <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
@@ -1167,24 +1553,36 @@
           <t>🔑</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Llavero con código Spotify escaneable, fondo personalizado.</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>Fondo personalizado · Diseño ambos lados</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>[{"unidades":1, "precio":3000}, {"unidades":2, "precio":5000}, {"unidades":3, "precio":6000}]</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="78" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -1198,24 +1596,38 @@
           <t>📱</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Mini tarjetas 5x7 con tu QR: ¡Escanéame!</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Precio único · Opalina lisa · Gramaje 250gr</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "5 x 7 cm": [{"unidades":100, "precio":5500}]
+}</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="78" customHeight="1">
       <c r="A23" s="5" t="n">
         <v>22</v>
       </c>
@@ -1229,18 +1641,33 @@
           <t>✨</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>Poleras blancas 100% poliéster con tu estampado.</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>100% poliéster · Poleras solo color blanco</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>{
+  "S - M - L": [{"unidades":1, "precio":8000}],
+  "XL - 2XL": [{"unidades":1, "precio":9000}]
+}</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1261,7 +1688,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -1379,338 +1806,338 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>3x3 cm</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="9" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>3x3 cm</t>
         </is>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="9" t="n">
         <v>13000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>3x3 cm</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="9" t="n">
         <v>22500</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>3x3 cm</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="8" t="n">
         <v>2000</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="9" t="n">
         <v>37500</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>4x4 cm</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="9" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>4x4 cm</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="9" t="n">
         <v>19950</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>4x4 cm</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="9" t="n">
         <v>35700</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>4x4 cm</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="8" t="n">
         <v>2000</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="9" t="n">
         <v>42000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>5x5 cm</t>
         </is>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="9" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>5x5 cm</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="9" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>5x5 cm</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="9" t="n">
         <v>38000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>5x5 cm</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="8" t="n">
         <v>2000</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="9" t="n">
         <v>48000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>6x6 cm</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="9" t="n">
         <v>9500</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>6x6 cm</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="9" t="n">
         <v>27500</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>6x6 cm</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="9" t="n">
         <v>42000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Stickers Troquelados</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>6x6 cm</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="8" t="n">
         <v>2000</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="9" t="n">
         <v>55900</v>
       </c>
     </row>
@@ -2030,212 +2457,212 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n">
+      <c r="A37" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>Tarjetas de Presentación</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>1 Cara</t>
         </is>
       </c>
-      <c r="D37" s="10" t="n">
+      <c r="D37" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="9" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n">
+      <c r="A38" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>Tarjetas de Presentación</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>1 Cara</t>
         </is>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="9" t="n">
         <v>14000</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n">
+      <c r="A39" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Tarjetas de Presentación</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>1 Cara</t>
         </is>
       </c>
-      <c r="D39" s="10" t="n">
+      <c r="D39" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="9" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Tarjetas de Presentación</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>1 Cara</t>
         </is>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="9" t="n">
         <v>35000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="n">
+      <c r="A41" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Tarjetas de Presentación</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>1 Cara</t>
         </is>
       </c>
-      <c r="D41" s="10" t="n">
+      <c r="D41" s="8" t="n">
         <v>2000</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="9" t="n">
         <v>55000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n">
+      <c r="A42" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>Tarjetas de Presentación</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>2 Caras</t>
         </is>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="9" t="n">
         <v>16000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n">
+      <c r="A43" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>Tarjetas de Presentación</t>
         </is>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>2 Caras</t>
         </is>
       </c>
-      <c r="D43" s="10" t="n">
+      <c r="D43" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="9" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n">
+      <c r="A44" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Tarjetas de Presentación</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>2 Caras</t>
         </is>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="E44" s="11" t="n">
+      <c r="E44" s="9" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n">
+      <c r="A45" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>Tarjetas de Presentación</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>2 Caras</t>
         </is>
       </c>
-      <c r="D45" s="10" t="n">
+      <c r="D45" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="E45" s="9" t="n">
         <v>48000</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="n">
+      <c r="A46" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr">
         <is>
           <t>Tarjetas de Presentación</t>
         </is>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>2 Caras</t>
         </is>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="8" t="n">
         <v>2000</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="9" t="n">
         <v>68000</v>
       </c>
     </row>
@@ -2450,212 +2877,212 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="10" t="n">
+      <c r="A57" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Talonario / Recetario</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>Media Carta 14x21,6</t>
         </is>
       </c>
-      <c r="D57" s="10" t="n">
+      <c r="D57" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="11" t="n">
+      <c r="E57" s="9" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="n">
+      <c r="A58" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Talonario / Recetario</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>Media Carta 14x21,6</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n">
+      <c r="D58" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E58" s="11" t="n">
+      <c r="E58" s="9" t="n">
         <v>22000</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="n">
+      <c r="A59" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Talonario / Recetario</t>
         </is>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>Media Carta 14x21,6</t>
         </is>
       </c>
-      <c r="D59" s="10" t="n">
+      <c r="D59" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E59" s="11" t="n">
+      <c r="E59" s="9" t="n">
         <v>35000</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="10" t="n">
+      <c r="A60" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Talonario / Recetario</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>Media Carta 14x21,6</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n">
+      <c r="D60" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E60" s="11" t="n">
+      <c r="E60" s="9" t="n">
         <v>52000</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="10" t="n">
+      <c r="A61" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Talonario / Recetario</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>Media Carta 14x21,6</t>
         </is>
       </c>
-      <c r="D61" s="10" t="n">
+      <c r="D61" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E61" s="11" t="n">
+      <c r="E61" s="9" t="n">
         <v>97000</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="n">
+      <c r="A62" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Talonario / Recetario</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>Carta 21,6x27,9</t>
         </is>
       </c>
-      <c r="D62" s="10" t="n">
+      <c r="D62" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="11" t="n">
+      <c r="E62" s="9" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="10" t="n">
+      <c r="A63" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Talonario / Recetario</t>
         </is>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>Carta 21,6x27,9</t>
         </is>
       </c>
-      <c r="D63" s="10" t="n">
+      <c r="D63" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E63" s="11" t="n">
+      <c r="E63" s="9" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="10" t="n">
+      <c r="A64" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Talonario / Recetario</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Carta 21,6x27,9</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n">
+      <c r="D64" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E64" s="11" t="n">
+      <c r="E64" s="9" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="10" t="n">
+      <c r="A65" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>Talonario / Recetario</t>
         </is>
       </c>
-      <c r="C65" s="10" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>Carta 21,6x27,9</t>
         </is>
       </c>
-      <c r="D65" s="10" t="n">
+      <c r="D65" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E65" s="11" t="n">
+      <c r="E65" s="9" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="n">
+      <c r="A66" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>Talonario / Recetario</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>Carta 21,6x27,9</t>
         </is>
       </c>
-      <c r="D66" s="10" t="n">
+      <c r="D66" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E66" s="11" t="n">
+      <c r="E66" s="9" t="n">
         <v>85000</v>
       </c>
     </row>
@@ -2828,338 +3255,338 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="10" t="n">
+      <c r="A75" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B75" s="10" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C75" s="10" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>Talla S 22x30</t>
         </is>
       </c>
-      <c r="D75" s="10" t="n">
+      <c r="D75" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E75" s="11" t="n">
+      <c r="E75" s="9" t="n">
         <v>15100</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="10" t="n">
+      <c r="A76" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B76" s="10" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>Talla S 22x30</t>
         </is>
       </c>
-      <c r="D76" s="10" t="n">
+      <c r="D76" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E76" s="11" t="n">
+      <c r="E76" s="9" t="n">
         <v>24500</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="n">
+      <c r="A77" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C77" s="10" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>Talla S 22x30</t>
         </is>
       </c>
-      <c r="D77" s="10" t="n">
+      <c r="D77" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E77" s="11" t="n">
+      <c r="E77" s="9" t="n">
         <v>47500</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="10" t="n">
+      <c r="A78" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B78" s="10" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>Talla S 22x30</t>
         </is>
       </c>
-      <c r="D78" s="10" t="n">
+      <c r="D78" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="E78" s="11" t="n">
+      <c r="E78" s="9" t="n">
         <v>76000</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="n">
+      <c r="A79" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B79" s="10" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C79" s="10" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>Talla M 30x32</t>
         </is>
       </c>
-      <c r="D79" s="10" t="n">
+      <c r="D79" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E79" s="11" t="n">
+      <c r="E79" s="9" t="n">
         <v>18100</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="n">
+      <c r="A80" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B80" s="10" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C80" s="10" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>Talla M 30x32</t>
         </is>
       </c>
-      <c r="D80" s="10" t="n">
+      <c r="D80" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E80" s="11" t="n">
+      <c r="E80" s="9" t="n">
         <v>29500</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="10" t="n">
+      <c r="A81" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B81" s="10" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C81" s="10" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>Talla M 30x32</t>
         </is>
       </c>
-      <c r="D81" s="10" t="n">
+      <c r="D81" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E81" s="11" t="n">
+      <c r="E81" s="9" t="n">
         <v>55000</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="n">
+      <c r="A82" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>Talla M 30x32</t>
         </is>
       </c>
-      <c r="D82" s="10" t="n">
+      <c r="D82" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="E82" s="11" t="n">
+      <c r="E82" s="9" t="n">
         <v>98000</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="n">
+      <c r="A83" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B83" s="10" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C83" s="10" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>Talla L 30x41</t>
         </is>
       </c>
-      <c r="D83" s="10" t="n">
+      <c r="D83" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E83" s="11" t="n">
+      <c r="E83" s="9" t="n">
         <v>21100</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="n">
+      <c r="A84" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>Talla L 30x41</t>
         </is>
       </c>
-      <c r="D84" s="10" t="n">
+      <c r="D84" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E84" s="11" t="n">
+      <c r="E84" s="9" t="n">
         <v>34000</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="n">
+      <c r="A85" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>Talla L 30x41</t>
         </is>
       </c>
-      <c r="D85" s="10" t="n">
+      <c r="D85" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E85" s="11" t="n">
+      <c r="E85" s="9" t="n">
         <v>65000</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="n">
+      <c r="A86" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B86" s="10" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C86" s="10" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Talla L 30x41</t>
         </is>
       </c>
-      <c r="D86" s="10" t="n">
+      <c r="D86" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="E86" s="11" t="n">
+      <c r="E86" s="9" t="n">
         <v>114000</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="10" t="n">
+      <c r="A87" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B87" s="10" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C87" s="10" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>Talla XL 38x48</t>
         </is>
       </c>
-      <c r="D87" s="10" t="n">
+      <c r="D87" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E87" s="11" t="n">
+      <c r="E87" s="9" t="n">
         <v>26850</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="10" t="n">
+      <c r="A88" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B88" s="10" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C88" s="10" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>Talla XL 38x48</t>
         </is>
       </c>
-      <c r="D88" s="10" t="n">
+      <c r="D88" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E88" s="11" t="n">
+      <c r="E88" s="9" t="n">
         <v>42000</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="10" t="n">
+      <c r="A89" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B89" s="10" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C89" s="10" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>Talla XL 38x48</t>
         </is>
       </c>
-      <c r="D89" s="10" t="n">
+      <c r="D89" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E89" s="11" t="n">
+      <c r="E89" s="9" t="n">
         <v>80000</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="10" t="n">
+      <c r="A90" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B90" s="10" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>Bolsas de Papel Personalizadas</t>
         </is>
       </c>
-      <c r="C90" s="10" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>Talla XL 38x48</t>
         </is>
       </c>
-      <c r="D90" s="10" t="n">
+      <c r="D90" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="E90" s="11" t="n">
+      <c r="E90" s="9" t="n">
         <v>140000</v>
       </c>
     </row>
@@ -3248,44 +3675,44 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="n">
+      <c r="A95" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B95" s="10" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>Tarjetas Cliente Frecuente</t>
         </is>
       </c>
-      <c r="C95" s="10" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>Tarjeta + Stickers</t>
         </is>
       </c>
-      <c r="D95" s="10" t="n">
+      <c r="D95" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E95" s="11" t="n">
+      <c r="E95" s="9" t="n">
         <v>19500</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="10" t="n">
+      <c r="A96" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B96" s="10" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>Tarjetas Cliente Frecuente</t>
         </is>
       </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>Tarjeta + Stickers</t>
         </is>
       </c>
-      <c r="D96" s="10" t="n">
+      <c r="D96" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="E96" s="11" t="n">
+      <c r="E96" s="9" t="n">
         <v>28000</v>
       </c>
     </row>
@@ -3332,107 +3759,107 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="10" t="n">
+      <c r="A99" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B99" s="10" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>Chapitas Personalizadas</t>
         </is>
       </c>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="C99" s="8" t="inlineStr">
         <is>
           <t>Unidades</t>
         </is>
       </c>
-      <c r="D99" s="10" t="n">
+      <c r="D99" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E99" s="11" t="n">
+      <c r="E99" s="9" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="n">
+      <c r="A100" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B100" s="10" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>Chapitas Personalizadas</t>
         </is>
       </c>
-      <c r="C100" s="10" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>Unidades</t>
         </is>
       </c>
-      <c r="D100" s="10" t="n">
+      <c r="D100" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="E100" s="11" t="n">
+      <c r="E100" s="9" t="n">
         <v>8600</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="n">
+      <c r="A101" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B101" s="10" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>Chapitas Personalizadas</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>Unidades</t>
         </is>
       </c>
-      <c r="D101" s="10" t="n">
+      <c r="D101" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E101" s="11" t="n">
+      <c r="E101" s="9" t="n">
         <v>11100</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="n">
+      <c r="A102" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B102" s="10" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>Chapitas Personalizadas</t>
         </is>
       </c>
-      <c r="C102" s="10" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>Unidades</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n">
+      <c r="D102" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E102" s="11" t="n">
+      <c r="E102" s="9" t="n">
         <v>15000</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="n">
+      <c r="A103" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B103" s="10" t="inlineStr">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>Chapitas Personalizadas</t>
         </is>
       </c>
-      <c r="C103" s="10" t="inlineStr">
+      <c r="C103" s="8" t="inlineStr">
         <is>
           <t>Unidades</t>
         </is>
       </c>
-      <c r="D103" s="10" t="n">
+      <c r="D103" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E103" s="11" t="n">
+      <c r="E103" s="9" t="n">
         <v>26000</v>
       </c>
     </row>
@@ -3521,44 +3948,44 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="10" t="n">
+      <c r="A108" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B108" s="10" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>Cédula de Identidad para Mascotas</t>
         </is>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t>Unidades</t>
         </is>
       </c>
-      <c r="D108" s="10" t="n">
+      <c r="D108" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E108" s="11" t="n">
+      <c r="E108" s="9" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="10" t="n">
+      <c r="A109" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B109" s="10" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>Cédula de Identidad para Mascotas</t>
         </is>
       </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>Unidades</t>
         </is>
       </c>
-      <c r="D109" s="10" t="n">
+      <c r="D109" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E109" s="11" t="n">
+      <c r="E109" s="9" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -3605,317 +4032,317 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="10" t="n">
+      <c r="A112" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B112" s="10" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C112" s="10" t="inlineStr">
+      <c r="C112" s="8" t="inlineStr">
         <is>
           <t>Espiga 1,5 cm</t>
         </is>
       </c>
-      <c r="D112" s="10" t="n">
+      <c r="D112" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E112" s="11" t="n">
+      <c r="E112" s="9" t="n">
         <v>3500</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="10" t="n">
+      <c r="A113" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B113" s="10" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C113" s="10" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
         <is>
           <t>Espiga 1,5 cm</t>
         </is>
       </c>
-      <c r="D113" s="10" t="n">
+      <c r="D113" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E113" s="11" t="n">
+      <c r="E113" s="9" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="10" t="n">
+      <c r="A114" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B114" s="10" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C114" s="10" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t>Espiga 1,5 cm</t>
         </is>
       </c>
-      <c r="D114" s="10" t="n">
+      <c r="D114" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E114" s="11" t="n">
+      <c r="E114" s="9" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="10" t="n">
+      <c r="A115" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B115" s="10" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C115" s="10" t="inlineStr">
+      <c r="C115" s="8" t="inlineStr">
         <is>
           <t>Espiga 1,5 cm</t>
         </is>
       </c>
-      <c r="D115" s="10" t="n">
+      <c r="D115" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="E115" s="11" t="n">
+      <c r="E115" s="9" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="10" t="n">
+      <c r="A116" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B116" s="10" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C116" s="10" t="inlineStr">
+      <c r="C116" s="8" t="inlineStr">
         <is>
           <t>Espiga 1,5 cm</t>
         </is>
       </c>
-      <c r="D116" s="10" t="n">
+      <c r="D116" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="E116" s="11" t="n">
+      <c r="E116" s="9" t="n">
         <v>23500</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="10" t="n">
+      <c r="A117" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B117" s="10" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C117" s="10" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
         <is>
           <t>Espiga 2 cm</t>
         </is>
       </c>
-      <c r="D117" s="10" t="n">
+      <c r="D117" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E117" s="11" t="n">
+      <c r="E117" s="9" t="n">
         <v>4500</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="10" t="n">
+      <c r="A118" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B118" s="10" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C118" s="10" t="inlineStr">
+      <c r="C118" s="8" t="inlineStr">
         <is>
           <t>Espiga 2 cm</t>
         </is>
       </c>
-      <c r="D118" s="10" t="n">
+      <c r="D118" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E118" s="11" t="n">
+      <c r="E118" s="9" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="10" t="n">
+      <c r="A119" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B119" s="10" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C119" s="10" t="inlineStr">
+      <c r="C119" s="8" t="inlineStr">
         <is>
           <t>Espiga 2 cm</t>
         </is>
       </c>
-      <c r="D119" s="10" t="n">
+      <c r="D119" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E119" s="11" t="n">
+      <c r="E119" s="9" t="n">
         <v>9500</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="10" t="n">
+      <c r="A120" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B120" s="10" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C120" s="10" t="inlineStr">
+      <c r="C120" s="8" t="inlineStr">
         <is>
           <t>Espiga 2 cm</t>
         </is>
       </c>
-      <c r="D120" s="10" t="n">
+      <c r="D120" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="E120" s="11" t="n">
+      <c r="E120" s="9" t="n">
         <v>20400</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="10" t="n">
+      <c r="A121" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B121" s="10" t="inlineStr">
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C121" s="10" t="inlineStr">
+      <c r="C121" s="8" t="inlineStr">
         <is>
           <t>Espiga 2 cm</t>
         </is>
       </c>
-      <c r="D121" s="10" t="n">
+      <c r="D121" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="E121" s="11" t="n">
+      <c r="E121" s="9" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="10" t="n">
+      <c r="A122" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B122" s="10" t="inlineStr">
+      <c r="B122" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C122" s="10" t="inlineStr">
+      <c r="C122" s="8" t="inlineStr">
         <is>
           <t>Espiga 2,5 cm</t>
         </is>
       </c>
-      <c r="D122" s="10" t="n">
+      <c r="D122" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="E122" s="11" t="n">
+      <c r="E122" s="9" t="n">
         <v>5500</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="10" t="n">
+      <c r="A123" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B123" s="10" t="inlineStr">
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="C123" s="8" t="inlineStr">
         <is>
           <t>Espiga 2,5 cm</t>
         </is>
       </c>
-      <c r="D123" s="10" t="n">
+      <c r="D123" s="8" t="n">
         <v>50</v>
       </c>
-      <c r="E123" s="11" t="n">
+      <c r="E123" s="9" t="n">
         <v>7000</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="10" t="n">
+      <c r="A124" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B124" s="10" t="inlineStr">
+      <c r="B124" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C124" s="10" t="inlineStr">
+      <c r="C124" s="8" t="inlineStr">
         <is>
           <t>Espiga 2,5 cm</t>
         </is>
       </c>
-      <c r="D124" s="10" t="n">
+      <c r="D124" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="E124" s="11" t="n">
+      <c r="E124" s="9" t="n">
         <v>11500</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="10" t="n">
+      <c r="A125" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B125" s="10" t="inlineStr">
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="C125" s="8" t="inlineStr">
         <is>
           <t>Espiga 2,5 cm</t>
         </is>
       </c>
-      <c r="D125" s="10" t="n">
+      <c r="D125" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="E125" s="11" t="n">
+      <c r="E125" s="9" t="n">
         <v>22500</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="10" t="n">
+      <c r="A126" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="B126" s="10" t="inlineStr">
+      <c r="B126" s="8" t="inlineStr">
         <is>
           <t>Etiquetas de Ropa</t>
         </is>
       </c>
-      <c r="C126" s="10" t="inlineStr">
+      <c r="C126" s="8" t="inlineStr">
         <is>
           <t>Espiga 2,5 cm</t>
         </is>
       </c>
-      <c r="D126" s="10" t="n">
+      <c r="D126" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="E126" s="11" t="n">
+      <c r="E126" s="9" t="n">
         <v>27500</v>
       </c>
     </row>
@@ -3941,23 +4368,23 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="10" t="n">
+      <c r="A128" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="B128" s="10" t="inlineStr">
+      <c r="B128" s="8" t="inlineStr">
         <is>
           <t>Morral</t>
         </is>
       </c>
-      <c r="C128" s="10" t="inlineStr">
+      <c r="C128" s="8" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="D128" s="10" t="n">
+      <c r="D128" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E128" s="11" t="n">
+      <c r="E128" s="9" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -4004,65 +4431,65 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="10" t="n">
+      <c r="A131" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B131" s="10" t="inlineStr">
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>Llavero Spotify</t>
         </is>
       </c>
-      <c r="C131" s="10" t="inlineStr">
+      <c r="C131" s="8" t="inlineStr">
         <is>
           <t>Unidades</t>
         </is>
       </c>
-      <c r="D131" s="10" t="n">
+      <c r="D131" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E131" s="11" t="n">
+      <c r="E131" s="9" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="10" t="n">
+      <c r="A132" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B132" s="10" t="inlineStr">
+      <c r="B132" s="8" t="inlineStr">
         <is>
           <t>Llavero Spotify</t>
         </is>
       </c>
-      <c r="C132" s="10" t="inlineStr">
+      <c r="C132" s="8" t="inlineStr">
         <is>
           <t>Unidades</t>
         </is>
       </c>
-      <c r="D132" s="10" t="n">
+      <c r="D132" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E132" s="11" t="n">
+      <c r="E132" s="9" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="10" t="n">
+      <c r="A133" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B133" s="10" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>Llavero Spotify</t>
         </is>
       </c>
-      <c r="C133" s="10" t="inlineStr">
+      <c r="C133" s="8" t="inlineStr">
         <is>
           <t>Unidades</t>
         </is>
       </c>
-      <c r="D133" s="10" t="n">
+      <c r="D133" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E133" s="11" t="n">
+      <c r="E133" s="9" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -4088,44 +4515,44 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="10" t="n">
+      <c r="A135" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B135" s="10" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>Poleras</t>
         </is>
       </c>
-      <c r="C135" s="10" t="inlineStr">
+      <c r="C135" s="8" t="inlineStr">
         <is>
           <t>S - M - L</t>
         </is>
       </c>
-      <c r="D135" s="10" t="n">
+      <c r="D135" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E135" s="11" t="n">
+      <c r="E135" s="9" t="n">
         <v>8000</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="10" t="n">
+      <c r="A136" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="B136" s="10" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>Poleras</t>
         </is>
       </c>
-      <c r="C136" s="10" t="inlineStr">
+      <c r="C136" s="8" t="inlineStr">
         <is>
           <t>XL - 2XL</t>
         </is>
       </c>
-      <c r="D136" s="10" t="n">
+      <c r="D136" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="E136" s="11" t="n">
+      <c r="E136" s="9" t="n">
         <v>9000</v>
       </c>
     </row>
@@ -4140,168 +4567,320 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="118" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>CATÁLOGO HEART GRAPHIC — INSTRUCCIONES</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr"/>
+      <c r="A2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Hoja 'productos':</t>
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Las celdas AMARILLAS son las que configuran cómo se ve el producto en la web.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>• id: número único, no repetir. Para agregar un producto usar el siguiente número libre.</t>
-        </is>
-      </c>
+      <c r="A4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
+          <t>Hoja 'productos' — una fila por producto:</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>• id: número único, no repetir. Para agregar un producto, usa el siguiente número libre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
           <t>• nombre: nombre del producto tal como se muestra en la página.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>• emoji: ícono de respaldo que se muestra mientras el producto no tenga imagen SVG subida.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>• descripcion: frase corta que aparece bajo el nombre del producto.</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>• notas: letra chica del producto (materiales, colores, condiciones). Separar ideas con ' · '.</t>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>• emoji: ícono de respaldo que se muestra si el producto no tiene ninguna foto.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>• imagen_principal (celdas amarillas): URL directa del SVG/PNG sin fondo (Cloudinary/ImgBB).</t>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>• categoria: en qué pestaña aparece. Escribe  vet  o  general . Si va en las dos: vet,general</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Vacío = la página muestra el emoji. Idealmente SVG sin fondo y de gran tamaño.</t>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>• descripcion: frase corta que aparece bajo el nombre y también arriba en la ficha.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>• activo: 'si' se muestra en la página, 'no' lo oculta sin borrar la fila (ej: sin stock).</t>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>• notas: letra chica del producto (materiales, medidas, condiciones).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr"/>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>• activo: 'si' se muestra en la página, 'no' la oculta sin borrar la fila.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Hoja 'precios':</t>
-        </is>
-      </c>
+      <c r="A13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>• Una fila por cada combinación producto + variante + cantidad.</t>
+          <t>• imagen_principal: nombre del archivo dentro de assets/productos/</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>• producto_id debe coincidir con el id de la hoja 'productos'. 'producto' es solo referencia visual.</t>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ejemplo:  19_mousepad.webp     Si está en una subcarpeta:  carnets_veterinarios/carnet_01.webp</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>• variante: columna de la tabla de precios (ej: '3x3 cm', '1 Cara', 'Talla M 30x32').</t>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  También acepta una URL completa que empiece con http.  Vacío = se muestra el emoji.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>• unidades: cantidad del tramo. precio: valor CLP de ese tramo.</t>
-        </is>
-      </c>
+      <c r="A17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>• Para cambiar un precio basta editar la celda; la página se actualiza al recargar.</t>
+          <t>• galeria: TODAS las fotos del producto, una lista entre corchetes. Pueden ser 1, 5 o 30.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr"/>
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ["19_mousepad.webp", "mousepad_2.webp", "mousepad_3.webp"]</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Ejemplo fila nueva en 'productos':   23 | Gorros Personalizados | 🧢 | Gorro bordado con tu logo | Solo blanco · Diseño gratis | https://...gorro.svg | si</t>
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Si el cliente no elige ningún color, estas fotos se van intercambiando solas en la ficha.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Ejemplo filas en 'precios':          23 | Gorros Personalizados | Unidades | 1 | 5000</t>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Vacío = usa solamente la imagen_principal.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr"/>
+      <c r="A22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>IMPORTANTE: no cambiar los nombres de las hojas ni de los encabezados (la página los lee tal cual).</t>
+          <t>• colores: los colores disponibles. Cada uno puede tener su propia foto.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Publicar: Archivo → Compartir → Publicar en la web (toda la planilla), y pegar el ID de la planilla</t>
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  {</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>en la constante SHEET_ID al inicio del archivo HTML.</t>
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "0": {"Color_hex":"#ffffff", "Color_name":"Blanco",  "url_img":"tazon_blanco.webp"},</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "1": {"Color_hex":"#f23b3b", "Color_name":"Rojo",    "url_img":"tazon_rojo.webp"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  }</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  url_img puede ir vacío ("") si todavía no tienes la foto de ese color: se muestra la galería.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Vacío = el producto no tiene selector de colores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>• cantidades: los tramos de precio. Dos formas según el producto:</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A) Producto SIN variantes — una lista simple:</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     [{"unidades":1, "precio":3500}, {"unidades":10, "precio":30000}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B) Producto CON variantes (tamaños, caras, tallas) — una variante por línea:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     {</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       "3x3 cm": [{"unidades":100, "precio":4000}, {"unidades":500, "precio":13000}],</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       "4x4 cm": [{"unidades":100, "precio":5500}, {"unidades":500, "precio":19950}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     }</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cuida los signos: cada { se cierra con } y cada [ se cierra con ]. Las comas van ENTRE elementos,</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  nunca antes de un cierre. Si el JSON queda mal escrito, la web ignora esa celda y usa la hoja 'precios'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>Hoja 'precios' — RESPALDO. Solo se usa si 'cantidades' está vacía o mal escrita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Una fila por combinación producto + variante + tramo. Mantiene el formato antiguo por si prefieres editar así.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Si un producto tiene 'cantidades' escrito, manda 'cantidades' y estas filas se ignoran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>IMPORTANTE: no cambiar los nombres de las hojas ni de las columnas (la primera fila).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>El orden de las columnas sí puede cambiar: la web las busca por su nombre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Publicar: Archivo → Compartir → Publicar en la web → toda la planilla. Luego pega el ID de la planilla</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>en la constante SHEET_ID al inicio del archivo index.html.</t>
         </is>
       </c>
     </row>

--- a/catalogo_heart_graphic.xlsx
+++ b/catalogo_heart_graphic.xlsx
@@ -127,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -177,6 +177,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -544,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -553,7 +556,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="56" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="56" customWidth="1" min="9" max="9"/>
     <col width="64" customWidth="1" min="10" max="10"/>
@@ -593,25 +596,30 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>material</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>imagen_principal</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>galeria</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>colores</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>cantidades</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>activo</t>
         </is>
@@ -646,9 +654,10 @@
           <t>Valores por mayor no válidos para tazones de colores/especiales (valor único $4.000) · Colores: blanco, rojo, verde, celeste, rosado y amarillo (mango e interior de color) · Diseño gratis</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr"/>
+      <c r="G2" s="19" t="n"/>
       <c r="H2" s="6" t="inlineStr"/>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr"/>
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>{
   "0": {"Color_hex":"#ffffff", "Color_name":"Blanco", "url_img":""},
@@ -660,14 +669,14 @@
 }</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>{
   "11 Onzas": [{"unidades":1, "precio":4000}, {"unidades":5, "precio":18500}, {"unidades":20, "precio":50000}, {"unidades":30, "precio":60000}]
 }</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -702,10 +711,15 @@
           <t>Para forma personalizada se requiere previa cotización · Adhesivo 135gr, full impresión · Diseño gratis</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Adhesivo", "detalle":["135 gramos", "Full impresión"]}</t>
+        </is>
+      </c>
       <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" s="6" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J3" s="6" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>{
   "3x3 cm": [{"unidades":100, "precio":4000}, {"unidades":500, "precio":13000}, {"unidades":1000, "precio":22500}, {"unidades":2000, "precio":37500}],
@@ -715,7 +729,7 @@
 }</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -750,10 +764,15 @@
           <t>Gramaje del papel: 135gr · Full impresiones, máxima calidad · Diseño gratis</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr"/>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Papel fotográfico", "detalle":["135 gramos", "Máxima calidad"]}</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="J4" s="6" t="inlineStr"/>
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t>{
   "Fotográfico 10x14,5": [{"unidades":500, "precio":24000}, {"unidades":1000, "precio":36000}, {"unidades":2000, "precio":60000}, {"unidades":4000, "precio":110000}, {"unidades":8000, "precio":155000}],
@@ -762,7 +781,7 @@
 }</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -797,10 +816,15 @@
           <t>Gramaje del papel: 250gr · Opalina lisa, full color · Tamaño 9x5,5 cm · Diseño gratis</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Opalina lisa", "detalle":["250 gramos", "Full color"]}</t>
+        </is>
+      </c>
       <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>{
   "1 Cara": [{"unidades":100, "precio":8000}, {"unidades":200, "precio":14000}, {"unidades":500, "precio":25000}, {"unidades":1000, "precio":35000}, {"unidades":2000, "precio":55000}],
@@ -808,7 +832,7 @@
 }</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -843,10 +867,15 @@
           <t>Grosor del imán: 0,4 · Adhesivo fotográfico full color · Diseño gratis</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Adhesivo fotográfico", "detalle":["Imán de 0,4 mm", "Full color"]}</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>{
   "Simple 5x5,5 cm": [{"unidades":100, "precio":13000}, {"unidades":300, "precio":25000}, {"unidades":500, "precio":40000}, {"unidades":1000, "precio":63000}, {"unidades":2000, "precio":110000}],
@@ -854,7 +883,7 @@
 }</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -889,10 +918,15 @@
           <t>100 hojas por talonario · Papel bond encolado, impresión alta calidad · Diseño gratis</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Papel bond encolado", "detalle":["100 hojas", "Alta calidad"]}</t>
+        </is>
+      </c>
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>{
   "Media Carta 14x21,6": [{"unidades":2, "precio":10000}, {"unidades":5, "precio":22000}, {"unidades":10, "precio":35000}, {"unidades":20, "precio":52000}, {"unidades":50, "precio":97000}],
@@ -900,7 +934,7 @@
 }</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -935,10 +969,15 @@
           <t>La medida indicada corresponde al carnet abierto · Papel 250gr, opalina lisa full color · Diseño gratis</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Opalina lisa", "detalle":["250 gramos", "Full color"]}</t>
+        </is>
+      </c>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr">
         <is>
           <t>{
   "Mini Carnet 20x14,5": [{"unidades":50, "precio":16000}, {"unidades":100, "precio":26000}, {"unidades":200, "precio":42000}, {"unidades":300, "precio":51000}],
@@ -946,7 +985,7 @@
 }</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -981,10 +1020,15 @@
           <t>Bolsa kraft blanca personalizada full color · Con manilla · Biodegradables · Solo color blanco disponible</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Kraft blanca", "detalle":["Biodegradable", "Con manilla"]}</t>
+        </is>
+      </c>
       <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr">
         <is>
           <t>{
   "Talla S 22x30": [{"unidades":30, "precio":15100}, {"unidades":50, "precio":24500}, {"unidades":100, "precio":47500}, {"unidades":200, "precio":76000}],
@@ -994,7 +1038,7 @@
 }</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1029,10 +1073,15 @@
           <t>Puede incluir QR personalizado (redes sociales, contactos, agradecimiento) · Adhesivo brillante troquelado · Diseño gratis</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Adhesivo brillante", "detalle":["Troquelado"]}</t>
+        </is>
+      </c>
       <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" s="6" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>{
   "3,5 x 10 cm": [{"unidades":100, "precio":10000}, {"unidades":300, "precio":19000}],
@@ -1040,7 +1089,7 @@
 }</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1075,17 +1124,18 @@
           <t>Tarjetas de 9x5,5 cm y stickers de 1,5 cm de diámetro · Diseño gratis</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="19" t="n"/>
       <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" s="6" t="inlineStr"/>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr">
         <is>
           <t>{
   "Tarjeta + Stickers": [{"unidades":100, "precio":19500}, {"unidades":300, "precio":28000}]
 }</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1120,17 +1170,22 @@
           <t>Papel adhesivo glossy 135gr · Full color · Diseño gratis</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Adhesivo glossy", "detalle":["135 gramos", "Full color"]}</t>
+        </is>
+      </c>
       <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" s="6" t="inlineStr"/>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr">
         <is>
           <t>{
   "10 x 8 cm": [{"unidades":100, "precio":13000}, {"unidades":300, "precio":25000}]
 }</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1165,15 +1220,20 @@
           <t>Diseño gratis al solicitar nuestro servicio</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr"/>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Metálica", "detalle":["Full color"]}</t>
+        </is>
+      </c>
       <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr">
         <is>
           <t>[{"unidades":10, "precio":5000}, {"unidades":20, "precio":8600}, {"unidades":30, "precio":11100}, {"unidades":50, "precio":15000}, {"unidades":100, "precio":26000}]</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1208,15 +1268,20 @@
           <t>Plástico PVC · Diseño gratis</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr"/>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Plástico PVC", "detalle":[]}</t>
+        </is>
+      </c>
       <c r="H14" s="6" t="inlineStr"/>
       <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>[{"unidades":1, "precio":3000}, {"unidades":10, "precio":25000}, {"unidades":20, "precio":40000}, {"unidades":30, "precio":53000}]</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1251,15 +1316,20 @@
           <t>Plástico PVC · Diseño ambos lados</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr"/>
+      <c r="G15" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Plástico PVC", "detalle":["Diseño ambos lados"]}</t>
+        </is>
+      </c>
       <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>[{"unidades":1, "precio":3000}, {"unidades":2, "precio":5000}]</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1294,15 +1364,20 @@
           <t>Plástico PVC rígido · Diseño ambos lados</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr"/>
+      <c r="G16" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"PVC rígido", "detalle":["Diseño ambos lados"]}</t>
+        </is>
+      </c>
       <c r="H16" s="6" t="inlineStr"/>
       <c r="I16" s="6" t="inlineStr"/>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>[{"unidades":1, "precio":3000}, {"unidades":2, "precio":5000}]</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1337,10 +1412,15 @@
           <t>Cinta espiga blanca sublimada · Full color personalizada · Diseño gratis</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr"/>
+      <c r="G17" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Cinta espiga blanca", "detalle":["Sublimada", "Full color"]}</t>
+        </is>
+      </c>
       <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr">
         <is>
           <t>{
   "Espiga 1,5 cm": [{"unidades":30, "precio":3500}, {"unidades":50, "precio":5000}, {"unidades":100, "precio":8000}, {"unidades":300, "precio":18000}, {"unidades":500, "precio":23500}],
@@ -1349,7 +1429,7 @@
 }</t>
         </is>
       </c>
-      <c r="K17" s="7" t="inlineStr">
+      <c r="L17" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1384,17 +1464,22 @@
           <t>Precio único · Estampado directo al vidrio · Stock rotativo</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr"/>
+      <c r="G18" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Vidrio", "detalle":["Estampado directo"]}</t>
+        </is>
+      </c>
       <c r="H18" s="6" t="inlineStr"/>
       <c r="I18" s="6" t="inlineStr"/>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>{
   "16 x 11 cm": [{"unidades":1, "precio":12000}]
 }</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1429,17 +1514,22 @@
           <t>Solo color blanco · Talla estándar · Cordones ajustables · 100% poliéster</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr"/>
+      <c r="G19" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"100% poliéster", "detalle":["Talla estándar", "Cordones ajustables"]}</t>
+        </is>
+      </c>
       <c r="H19" s="6" t="inlineStr"/>
       <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>{
   "Unidad": [{"unidades":1, "precio":1800}]
 }</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1474,17 +1564,18 @@
           <t>Sobre las 10 unidades: $2.500 c/u · Diseño gratis</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr"/>
+      <c r="G20" s="19" t="n"/>
       <c r="H20" s="6" t="inlineStr"/>
       <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr">
+      <c r="J20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr">
         <is>
           <t>{
   "21 x 17 cm": [{"unidades":1, "precio":3000}, {"unidades":10, "precio":25000}]
 }</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1519,15 +1610,16 @@
           <t>Fondo personalizado · Diseño ambos lados</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
+      <c r="G21" s="19" t="n"/>
       <c r="H21" s="6" t="inlineStr"/>
       <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="J21" s="6" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>[{"unidades":1, "precio":3000}, {"unidades":2, "precio":5000}, {"unidades":3, "precio":6000}]</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
+      <c r="L21" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1562,17 +1654,22 @@
           <t>Precio único · Opalina lisa · Gramaje 250gr</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr"/>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"Opalina lisa", "detalle":["250 gramos"]}</t>
+        </is>
+      </c>
       <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr">
         <is>
           <t>{
   "5 x 7 cm": [{"unidades":100, "precio":5500}]
 }</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1607,10 +1704,15 @@
           <t>100% poliéster · Poleras solo color blanco</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr"/>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>{"icono":"", "titulo":"100% poliéster", "detalle":["Solo color blanco"]}</t>
+        </is>
+      </c>
       <c r="H23" s="6" t="inlineStr"/>
       <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr">
         <is>
           <t>{
   "S - M - L": [{"unidades":1, "precio":8000}],
@@ -1618,7 +1720,7 @@
 }</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1635,7 +1737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A56"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -1761,73 +1863,73 @@
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>• imagen_principal: la URL de la foto principal. Pega la dirección completa:</t>
+          <t>• material: la ficha de material que se ve en la tarjeta y en el modal.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  https://tu-almacenamiento.com/fotos/mousepad.webp</t>
+          <t xml:space="preserve">  {"icono":"https://tu-almacen.com/iconos/adhesivo.svg", "titulo":"Adhesivo fotográfico", "detalle":["115 gramos","Alta calidad"]}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vacío = se muestra el emoji.</t>
+          <t xml:space="preserve">  icono: URL de un SVG (o PNG). Puede ir vacío y se muestra solo el texto.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr"/>
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  titulo: el nombre del material, en grande. detalle: las líneas chicas, tantas como quieras.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>• galeria: TODAS las fotos del producto, una lista entre corchetes. Pueden ser 1, 5 o 30.</t>
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  detalle también acepta un texto solo: "115 gramos · Alta calidad" (se corta en los ·).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  [</t>
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Si el producto tiene MÁS DE UN material, pon una lista: [{...}, {...}]</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "https://tu-almacenamiento.com/fotos/mousepad-1.webp",</t>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  En vez de icono puedes usar "emoji":"📄" como atajo mientras no tengas el SVG.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "https://tu-almacenamiento.com/fotos/mousepad-2.webp"</t>
-        </is>
-      </c>
+      <c r="A27" s="14" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ]</t>
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>• imagen_principal: la URL de la foto principal. Pega la dirección completa:</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Si el cliente no elige ningún color, estas fotos se van intercambiando solas en la ficha.</t>
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  https://tu-almacenamiento.com/fotos/mousepad.webp</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vacío = usa solamente la imagen_principal.</t>
+          <t xml:space="preserve">  Vacío = se muestra el emoji.</t>
         </is>
       </c>
     </row>
@@ -1837,49 +1939,49 @@
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>• colores: los colores disponibles. Cada uno puede tener su propia foto.</t>
+          <t>• galeria: TODAS las fotos del producto, una lista entre corchetes. Pueden ser 1, 5 o 30.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  {</t>
+          <t xml:space="preserve">  [</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "0": {"Color_hex":"#ffffff", "Color_name":"Blanco", "url_img":"https://.../tazon-blanco.webp"},</t>
+          <t xml:space="preserve">    "https://tu-almacenamiento.com/fotos/mousepad-1.webp",</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    "1": {"Color_hex":"#f23b3b", "Color_name":"Rojo",   "url_img":""}</t>
+          <t xml:space="preserve">    "https://tu-almacenamiento.com/fotos/mousepad-2.webp"</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  }</t>
+          <t xml:space="preserve">  ]</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  url_img puede ir vacío ("") si todavía no tienes la foto de ese color: se muestra la galería.</t>
+          <t xml:space="preserve">  Si el cliente no elige ningún color, estas fotos se van intercambiando solas en la ficha.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vacío = el producto no tiene selector de colores.</t>
+          <t xml:space="preserve">  Vacío = usa solamente la imagen_principal.</t>
         </is>
       </c>
     </row>
@@ -1889,109 +1991,161 @@
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>• cantidades: los tramos de precio. Dos formas según el producto:</t>
+          <t>• colores: los colores disponibles. Cada uno puede tener su propia foto.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A) Producto SIN variantes — una lista simple:</t>
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  {</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">     [{"unidades":1, "precio":3500}, {"unidades":10, "precio":30000}]</t>
+          <t xml:space="preserve">    "0": {"Color_hex":"#ffffff", "Color_name":"Blanco", "url_img":"https://.../tazon-blanco.webp"},</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B) Producto CON variantes (tamaños, caras, tallas) — una variante por línea:</t>
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "1": {"Color_hex":"#f23b3b", "Color_name":"Rojo",   "url_img":""}</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">     {</t>
+          <t xml:space="preserve">  }</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       "3x3 cm": [{"unidades":100, "precio":4000}, {"unidades":500, "precio":13000}],</t>
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  url_img puede ir vacío ("") si todavía no tienes la foto de ese color: se muestra la galería.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       "4x4 cm": [{"unidades":100, "precio":5500}, {"unidades":500, "precio":19950}]</t>
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Vacío = el producto no tiene selector de colores.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     }</t>
-        </is>
-      </c>
+      <c r="A47" s="14" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cuida los signos: cada { se cierra con } y cada [ se cierra con ]. Las comas van ENTRE elementos,</t>
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>• cantidades: los tramos de precio. Dos formas según el producto:</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  nunca antes de un cierre. Si el JSON queda mal escrito, ese producto no se muestra: revisa la consola del navegador (F12).</t>
+          <t xml:space="preserve">  A) Producto SIN variantes — una lista simple:</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="inlineStr"/>
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     [{"unidades":1, "precio":3500}, {"unidades":10, "precio":30000}]</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>Los precios salen SOLO de la columna 'cantidades'. No hay hoja de respaldo.</t>
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B) Producto CON variantes (tamaños, caras, tallas) — una variante por línea:</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Si una celda 'cantidades' queda mal escrita, ese producto NO aparece en la web y el aviso sale en la consola del navegador (F12).</t>
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     {</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="14" t="inlineStr"/>
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       "3x3 cm": [{"unidades":100, "precio":4000}, {"unidades":500, "precio":13000}],</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>IMPORTANTE: no cambiar los nombres de las hojas ni de las columnas (la primera fila).</t>
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       "4x4 cm": [{"unidades":100, "precio":5500}, {"unidades":500, "precio":19950}]</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="14" t="inlineStr">
-        <is>
-          <t>El orden de las columnas sí puede cambiar: la web las busca por su nombre.</t>
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     }</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cuida los signos: cada { se cierra con } y cada [ se cierra con ]. Las comas van ENTRE elementos,</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  nunca antes de un cierre. Si el JSON queda mal escrito, ese producto no se muestra: revisa la consola del navegador (F12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>Los precios salen SOLO de la columna 'cantidades'. No hay hoja de respaldo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Si una celda 'cantidades' queda mal escrita, ese producto NO aparece en la web y el aviso sale en la consola del navegador (F12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>IMPORTANTE: no cambiar los nombres de las hojas ni de las columnas (la primera fila).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>El orden de las columnas sí puede cambiar: la web las busca por su nombre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>Todas las fotos van por URL completa (https://...). No se usan archivos locales.</t>
         </is>

--- a/catalogo_heart_graphic.xlsx
+++ b/catalogo_heart_graphic.xlsx
@@ -127,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -181,6 +181,15 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -256,6 +265,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Heart Graphic</author>
+  </authors>
+  <commentList>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>% de descuento por defecto del producto (0–90). 0 o vacío = sin descuento. Se aplica a todos los tramos de 'cantidades' y en la web se ve el precio viejo tachado y el nuevo.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -547,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +585,8 @@
     <col width="56" customWidth="1" min="9" max="9"/>
     <col width="64" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -619,7 +645,12 @@
           <t>cantidades</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="20" t="inlineStr">
+        <is>
+          <t>descuento</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>activo</t>
         </is>
@@ -676,7 +707,10 @@
 }</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -729,7 +763,10 @@
 }</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L3" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -781,7 +818,10 @@
 }</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="L4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -832,7 +872,10 @@
 }</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -883,7 +926,10 @@
 }</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -934,7 +980,10 @@
 }</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="L7" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -985,7 +1034,10 @@
 }</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1038,7 +1090,10 @@
 }</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="L9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1089,7 +1144,10 @@
 }</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1135,7 +1193,10 @@
 }</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="L11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1185,7 +1246,10 @@
 }</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="L12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1233,7 +1297,10 @@
           <t>[{"unidades":10, "precio":5000}, {"unidades":20, "precio":8600}, {"unidades":30, "precio":11100}, {"unidades":50, "precio":15000}, {"unidades":100, "precio":26000}]</t>
         </is>
       </c>
-      <c r="L13" s="7" t="inlineStr">
+      <c r="L13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1281,7 +1348,10 @@
           <t>[{"unidades":1, "precio":3000}, {"unidades":10, "precio":25000}, {"unidades":20, "precio":40000}, {"unidades":30, "precio":53000}]</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1329,7 +1399,10 @@
           <t>[{"unidades":1, "precio":3000}, {"unidades":2, "precio":5000}]</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1377,7 +1450,10 @@
           <t>[{"unidades":1, "precio":3000}, {"unidades":2, "precio":5000}]</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1429,7 +1505,10 @@
 }</t>
         </is>
       </c>
-      <c r="L17" s="7" t="inlineStr">
+      <c r="L17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1479,7 +1558,10 @@
 }</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="L18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1529,7 +1611,10 @@
 }</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="L19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1575,7 +1660,10 @@
 }</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="L20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1619,7 +1707,10 @@
           <t>[{"unidades":1, "precio":3000}, {"unidades":2, "precio":5000}, {"unidades":3, "precio":6000}]</t>
         </is>
       </c>
-      <c r="L21" s="7" t="inlineStr">
+      <c r="L21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1669,7 +1760,10 @@
 }</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="L22" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>si</t>
         </is>
@@ -1720,14 +1814,24 @@
 }</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="L23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Descuento" error="Escribe un número entero entre 0 y 90 (es un porcentaje)." type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>90</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1737,7 +1841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -2116,36 +2220,71 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Los precios salen SOLO de la columna 'cantidades'. No hay hoja de respaldo.</t>
+          <t>• descuento: porcentaje de descuento POR DEFECTO del producto (número entero, sin el signo %). Ej: 15</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Si una celda 'cantidades' queda mal escrita, ese producto NO aparece en la web y el aviso sale en la consola del navegador (F12).</t>
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Se aplica a TODOS los tramos de 'cantidades' del producto. En la web se ve el precio viejo tachado,</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="14" t="inlineStr"/>
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  el precio nuevo y la etiqueta -15%. El precio nuevo se redondea a los $10 más cercanos.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="15" t="inlineStr">
-        <is>
-          <t>IMPORTANTE: no cambiar los nombres de las hojas ni de las columnas (la primera fila).</t>
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  El mensaje de WhatsApp/Instagram también lleva el precio con descuento (y el precio anterior).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  0 o vacío = sin descuento (se muestra el precio normal, sin tachar nada).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>Los precios salen SOLO de la columna 'cantidades'. No hay hoja de respaldo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Si una celda 'cantidades' queda mal escrita, ese producto NO aparece en la web y el aviso sale en la consola del navegador (F12).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>IMPORTANTE: no cambiar los nombres de las hojas ni de las columnas (la primera fila).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
           <t>El orden de las columnas sí puede cambiar: la web las busca por su nombre.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="14" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
         <is>
           <t>Todas las fotos van por URL completa (https://...). No se usan archivos locales.</t>
         </is>

--- a/catalogo_heart_graphic.xlsx
+++ b/catalogo_heart_graphic.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -587,6 +587,7 @@
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -653,6 +654,11 @@
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>activo</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>tarjeta_inicio</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1830,10 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation sqref="N2:N200" type="list" allowBlank="1" showErrorMessage="1" errorTitle="tarjeta_inicio" error="Escribe si o no.">
+      <formula1>"si,no"</formula1>
+    </dataValidation>
     <dataValidation sqref="L2:L200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Descuento" error="Escribe un número entero entre 0 y 90 (es un porcentaje)." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>90</formula2>
@@ -1841,7 +1850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -2290,6 +2299,30 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">• tarjeta_inicio: 'si' = el producto rota en la tarjeta grande de la ENTRADA SALUD (inicio de la página).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Solo afecta esa tarjeta: no cambia el carrusel ni los demás destacados. Vacío o 'no' = no aparece en ella.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Si ningún producto tiene 'si', la tarjeta rota por todo el catálogo. Los planners no entran (tienen su propia planilla).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
